--- a/九龙-九龙站-天玺/天玺_销控明细表.xlsx
+++ b/九龙-九龙站-天玺/天玺_销控明细表.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,6 +132,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -213,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -281,7 +286,10 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1291,7 +1299,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1341,7 +1349,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1587,7 +1595,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1783,7 +1791,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -35735,7 +35743,7 @@
       </c>
       <c r="F760" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G760" s="3" t="inlineStr">
@@ -35831,7 +35839,7 @@
       </c>
       <c r="F762" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G762" s="3" t="inlineStr">
@@ -35973,7 +35981,7 @@
       </c>
       <c r="F765" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G765" s="3" t="inlineStr">
@@ -38921,12 +38929,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -39109,7 +39117,7 @@
           <t>C | 1361呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -39117,7 +39125,7 @@
           <t>D | 1422呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -39140,7 +39148,7 @@
           <t>B | 693呎 (2房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39179,7 +39187,7 @@
           <t>B | 693呎 (2房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -39564,7 +39572,7 @@
 (18年-12月-23日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 693呎 (2房)
 $5527万
@@ -39580,7 +39588,7 @@
 (23年-12月-21日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>D | 1422呎 (4+房)
 $10342万
@@ -47018,12 +47026,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -47085,7 +47093,7 @@
           <t>A | 1327呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -47102,7 +47110,7 @@
           <t>D | 1452呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr"/>
@@ -47134,7 +47142,7 @@
           <t>C | 2890呎 (4+房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">

--- a/九龙-九龙站-天玺/天玺_销控明细表.xlsx
+++ b/九龙-九龙站-天玺/天玺_销控明细表.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,11 +132,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -218,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -286,10 +281,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1299,7 +1291,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1349,7 +1341,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1595,7 +1587,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1791,7 +1783,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -35743,7 +35735,7 @@
       </c>
       <c r="F760" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G760" s="3" t="inlineStr">
@@ -35839,7 +35831,7 @@
       </c>
       <c r="F762" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G762" s="3" t="inlineStr">
@@ -35981,7 +35973,7 @@
       </c>
       <c r="F765" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G765" s="3" t="inlineStr">
@@ -38929,12 +38921,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -39117,7 +39109,7 @@
           <t>C | 1361呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -39125,7 +39117,7 @@
           <t>D | 1422呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39148,7 +39140,7 @@
           <t>B | 693呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -39187,7 +39179,7 @@
           <t>B | 693呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -39572,7 +39564,7 @@
 (18年-12月-23日)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 693呎 (2房)
 $5527万
@@ -39588,7 +39580,7 @@
 (23年-12月-21日)</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 1422呎 (4+房)
 $10342万
@@ -47026,12 +47018,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -47093,7 +47085,7 @@
           <t>A | 1327呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -47110,7 +47102,7 @@
           <t>D | 1452呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr"/>
@@ -47142,7 +47134,7 @@
           <t>C | 2890呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">

--- a/九龙-九龙站-天玺/天玺_销控明细表.xlsx
+++ b/九龙-九龙站-天玺/天玺_销控明细表.xlsx
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>20662200</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>30839</v>
+        <v>30565</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -40950,9 +40950,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>E | 670呎 (2房)
+          <t>E | 676呎 (2房)
 $2066万
-$30,839/呎
+$30,565/呎
 (12年-04月-17日)</t>
         </is>
       </c>
